--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T09:28:26+00:00</t>
+    <t>2023-10-16T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule-availability-time</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-schedule-availability-time</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,7 +257,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-schedule-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-schedule-type</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -326,7 +326,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-availability-time-rule</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-availability-time-rule</t>
   </si>
   <si>
     <t>Extension.extension:rrule.extension:freq.value[x].id</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -983,7 +983,7 @@
 </t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-core-schedule-unavailability-reason</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-schedule-unavailability-reason</t>
   </si>
   <si>
     <t>Extension.extension:created</t>
@@ -1363,7 +1363,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.84765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3869" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3870" uniqueCount="330">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T15:11:22+00:00</t>
+    <t>2023-11-21T10:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,9 +981,6 @@
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-schedule-unavailability-reason</t>
   </si>
   <si>
     <t>Extension.extension:created</t>
@@ -1363,7 +1360,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.27734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -12352,11 +12349,13 @@
         <v>74</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y106" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z106" t="s" s="2">
-        <v>316</v>
+        <v>74</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12394,13 +12393,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>87</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>74</v>
@@ -12425,10 +12424,10 @@
         <v>89</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12499,7 +12498,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>98</v>
@@ -12602,7 +12601,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>100</v>
@@ -12705,7 +12704,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>102</v>
@@ -12748,7 +12747,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>74</v>
@@ -12810,7 +12809,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>110</v>
@@ -12913,13 +12912,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>87</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>74</v>
@@ -13018,7 +13017,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>98</v>
@@ -13121,7 +13120,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>100</v>
@@ -13224,7 +13223,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>102</v>
@@ -13267,7 +13266,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>74</v>
@@ -13329,7 +13328,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>110</v>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T10:12:17+00:00</t>
+    <t>2024-02-05T11:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -374,7 +374,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-schedule-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-schedule-type</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -443,7 +443,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-availability-time-rule</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-availability-time-rule</t>
   </si>
   <si>
     <t>Extension.extension:rrule.extension:freq.value[x].id</t>
@@ -1374,7 +1374,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.1875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T11:48:42+00:00</t>
+    <t>2024-02-12T13:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T13:27:08+00:00</t>
+    <t>2024-02-12T14:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:02:40+00:00</t>
+    <t>2024-02-26T11:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:03:57+00:00</t>
+    <t>2024-03-04T10:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T10:55:37+00:00</t>
+    <t>2024-03-11T09:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T09:42:54+00:00</t>
+    <t>2024-03-11T10:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:34:02+00:00</t>
+    <t>2024-03-20T14:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/ig/main/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:49:36+00:00</t>
+    <t>2024-03-21T08:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
